--- a/261022_회의록_소울푸드베트남전류검토.xlsx
+++ b/261022_회의록_소울푸드베트남전류검토.xlsx
@@ -567,7 +567,7 @@
         <is>
           <t>· 소울푸드(수입원)의 베트남 광닌 공장 50g 전류·튀김(브랜드 월남간)을 우리 전용 포장으로 도입하는 안 검토
 · 1kg×5봉 100박스부터 시험 통관 가능, 샘플은 아이스박스로 제공 → 단가·MOQ는 아직 논의 전(전체 견적 요청)
-· 서울 급식은 렌시푸드가 권한을 가져 교통정리 필요 → 렌시 의견 확인 후 MD 수요 조사 진행
+· 랜시푸드가 총판권을 갖고 아워홈에 공급 중 → 판매권 정리가 선행 필요(소울푸드가 차주 수요일 10/28 진행)
 · 다음 단계: 각 MD 수요 확인, 온라인 판매가 조사, CJ대한통운 냉동 물류 협의 결과 확인</t>
         </is>
       </c>
@@ -600,7 +600,7 @@
       </c>
       <c r="D9" s="7" t="n"/>
     </row>
-    <row r="10" ht="60" customHeight="1">
+    <row r="10" ht="75" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
           <t>업체·제품</t>
@@ -608,7 +608,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>소울푸드: 수입원·유통전문판매원(직원 3명). 베트남 광닌 공장과 약 3년 반 거래(설비·X-ray 완비, 베트남 HACCP·ISO 보유). 30g은 사옹원 강세·단가 경쟁이라 50g 전류로 차별화</t>
+          <t>소울푸드: 수입원·유통전문판매원(직원 3명). 베트남 광닌 공장과 약 3년 반 거래(소울푸드 전체 매출 월 약 4억 원 / 설비·X-ray 완비, 베트남 HACCP·ISO 보유). 30g은 사옹원 강세·단가 경쟁이라 50g 전류로 차별화</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="D12" s="7" t="n"/>
     </row>
-    <row r="13" ht="60" customHeight="1">
+    <row r="13" ht="75" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
           <t>유통 구조</t>
@@ -662,12 +662,12 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>대구 온라인 총판(B2C), 서울 급식은 렌시푸드. CJ프레시원은 대구센터만 입고(양산 코드 최근 개방, 물량 적을 전망). 아워홈 입고 확실, 대기업은 도매 경유. 중·고교 급식 호조, 군납은 단가 위주라 탈락</t>
+          <t>대구 온라인 총판(B2C), 서울 급식은 랜시푸드가 총판권 보유. CJ프레시원은 대구센터만 입고(양산 코드 최근 개방, 물량 적을 전망). 아워홈은 랜시푸드가 공급 중, 대기업은 도매 경유. 중·고교 급식 호조, 군납은 단가 위주라 탈락</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>렌시 매출 '1억 5천' 월/연 확인 필요</t>
+          <t>랜시 월 약 1.5억 원 = 소울푸드 월 약 4억 원의 약 38%(1.5÷4)</t>
         </is>
       </c>
       <c r="D13" s="7" t="n"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>렌시에는 수입원에 준하는 단가, 도매는 그 위에 가산, 소비자용은 더 높게 → 판매가 준수 요구. 환율 1,400→1,560원 구간을 단가 인상 없이 약 6개월 감수(월 600~700만 원 손실 언급)</t>
+          <t>랜시에는 수입원에 준하는 단가, 도매는 그 위에 가산, 소비자용은 더 높게 → 판매가 준수 요구. 환율 1,400→1,560원 구간을 단가 인상 없이 약 6개월 감수(월 600~700만 원 손실 언급)</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="D15" s="7" t="n"/>
     </row>
-    <row r="16" ht="60" customHeight="1">
+    <row r="16" ht="75" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
           <t>쟁점</t>
@@ -716,7 +716,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>렌시와 권한 중복 우려, 급식 영업 전 렌시 의견 필요. 우리 도매 조직 없음(남양주 창고 냉동 불가, 이천 센터는 냉동·냉장 보유). 온라인은 총판이 쿠팡 등 운영해 여지 적음</t>
+          <t>랜시푸드 총판권·아워홈 공급과 판매권이 겹침 → 소울푸드가 차주 수요일(10/28) 정리 예정, 정리 전 급식 영업 보류. 우리 도매 조직 없음(남양주 창고 냉동 불가, 이천 센터는 냉동·냉장 보유). 온라인은 총판이 쿠팡 등 운영해 여지 적음</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>각 MD(웰스토리·아워홈·현대그린푸드·푸드머스·푸디스트·CJ프레시웨이·동원·신세계)에 50g 수요 확인, 렌시 경유 입고처 파악</t>
+          <t>각 MD(웰스토리·아워홈·현대그린푸드·푸드머스·푸디스트·CJ프레시웨이·동원·신세계)에 50g 수요 확인, 랜시 경유 입고처 파악</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>렌시 의견 확인(소울푸드 대표가 수요일 푸디스트 방문 시 문의)</t>
+          <t>판매권(총판권) 정리 결과 확인 — 소울푸드가 랜시푸드와 조율(푸디스트 담당자 방문 시 문의 포함)</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>수요일</t>
+          <t>10/28(수)</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       <c r="A30" s="6" t="inlineStr">
         <is>
           <t>· 회의 일시·장소·참석자 이름(녹취는 "참석자 1~4"로만 표기, 참석자 1이 소울푸드 대표로 보임)
-· 렌시푸드 매출 '1억 5천'이 월/연 어느 쪽인지, 웰스토리 경유 업체명(녹취상 불명확)
+· 웰스토리 경유 업체명(녹취상 불명확), 매출은 구두 언급 수치(랜시 월 약 1.5억·전체 월 약 4억)
 · 사옹원·상호원 표기 혼재, 가격·MOQ 수치는 녹취에 없음
 · 양산·이천 센터 관련 발언의 정확한 의미</t>
         </is>
